--- a/docs/build/lakeshore-enterprise-context/source/04_finance_performance/value_pools.xlsx
+++ b/docs/build/lakeshore-enterprise-context/source/04_finance_performance/value_pools.xlsx
@@ -489,7 +489,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26.8</v>
+        <v>26.1</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -498,7 +498,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12-18m</t>
+          <t>6-12m</t>
         </is>
       </c>
     </row>
@@ -514,11 +514,11 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>32</v>
+        <v>35.1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -539,16 +539,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>37.3</v>
+        <v>7.4</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>12-18m</t>
+          <t>6-12m</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.1</v>
+        <v>35.8</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>30.6</v>
+        <v>13.6</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -614,11 +614,11 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>21.4</v>
+        <v>60.8</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -639,16 +639,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>47</v>
+        <v>45.2</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>12-18m</t>
+          <t>18-24m</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>33.4</v>
+        <v>37.4</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
